--- a/performance-dashboard/archive/交易表现_20260305.xlsx
+++ b/performance-dashboard/archive/交易表现_20260305.xlsx
@@ -1673,52 +1673,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>¥989,672.84</t>
+          <t>¥988,948.10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>¥-10,327.16</t>
+          <t>¥-11,051.90</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-17.04%</t>
+          <t>-17.03%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-2.051</v>
+        <v>-2.121</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-0.0776%</t>
+          <t>-0.0773%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>10.5014%</t>
+          <t>10.1194%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>20260304</t>
+          <t>20260305</t>
         </is>
       </c>
     </row>
@@ -3653,52 +3653,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>¥989,672.84</t>
+          <t>¥988,948.10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>¥-10,327.16</t>
+          <t>¥-11,051.90</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-17.04%</t>
+          <t>-17.03%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2.051</v>
+        <v>-2.121</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.0776%</t>
+          <t>-0.0773%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10.5014%</t>
+          <t>10.1194%</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>20260304</t>
+          <t>20260305</t>
         </is>
       </c>
     </row>
